--- a/artfynd/A 58964-2025 artfynd.xlsx
+++ b/artfynd/A 58964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744312</v>
       </c>
       <c r="B2" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58964-2025 artfynd.xlsx
+++ b/artfynd/A 58964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744312</v>
       </c>
       <c r="B2" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58964-2025 artfynd.xlsx
+++ b/artfynd/A 58964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744312</v>
       </c>
       <c r="B2" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58964-2025 artfynd.xlsx
+++ b/artfynd/A 58964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744312</v>
       </c>
       <c r="B2" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58964-2025 artfynd.xlsx
+++ b/artfynd/A 58964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744312</v>
       </c>
       <c r="B2" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58964-2025 artfynd.xlsx
+++ b/artfynd/A 58964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744312</v>
       </c>
       <c r="B2" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58964-2025 artfynd.xlsx
+++ b/artfynd/A 58964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744312</v>
       </c>
       <c r="B2" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58964-2025 artfynd.xlsx
+++ b/artfynd/A 58964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744312</v>
       </c>
       <c r="B2" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58964-2025 artfynd.xlsx
+++ b/artfynd/A 58964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744312</v>
       </c>
       <c r="B2" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
